--- a/analise_eua/semicondutores/intel/intc_10q.xlsx
+++ b/analise_eua/semicondutores/intel/intc_10q.xlsx
@@ -433,65 +433,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44835</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44744</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44653</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44464</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44100</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
     </row>
@@ -502,60 +505,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>16853</v>
+      </c>
+      <c r="C2" t="n">
         <v>15542</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>19794</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>11563</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>12101</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>15301</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>17986</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>14388</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>17409</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>15908</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>19302</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>18030</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>22654</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>32481</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>4004</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3014</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>2417</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>2987</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4791</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1296</v>
       </c>
     </row>
@@ -566,60 +572,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4033</v>
+      </c>
+      <c r="C3" t="n">
         <v>4066</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>3202</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2360</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>3064</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>3121</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>3131</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3323</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2843</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2996</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3847</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>7469</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>6063</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>7074</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8400</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>7460</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>7208</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>7140</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7441</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>8455</v>
       </c>
     </row>
@@ -630,60 +639,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>12492</v>
+      </c>
+      <c r="C4" t="n">
         <v>12426</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>11489</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>11377</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>12281</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>12062</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>11244</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>11494</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>11466</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>11984</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>12993</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>12831</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>12174</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>11935</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>9798</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>8817</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>8487</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>9273</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>8969</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>9246</v>
       </c>
     </row>
@@ -694,60 +706,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>10961</v>
+      </c>
+      <c r="C5" t="n">
         <v>12876</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>6105</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>8432</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>5741</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>6868</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>7181</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>6480</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>4472</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>4119</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>3940</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6348</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5275</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>4627</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>2073</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>2421</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2124</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>2119</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2165</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>2997</v>
       </c>
     </row>
@@ -758,60 +773,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>57213</v>
+      </c>
+      <c r="C6" t="n">
         <v>62157</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>51731</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>43375</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>42134</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>46137</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>50829</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>42608</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>43811</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>43356</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>48314</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>49263</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>50588</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>62568</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>61304</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>49372</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>45773</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>36785</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>44390</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>41501</v>
       </c>
     </row>
@@ -822,60 +840,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>105741</v>
+      </c>
+      <c r="C7" t="n">
         <v>104458</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>105047</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>109510</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>109763</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>104248</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>103398</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>99924</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>93352</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>90945</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>85734</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>75763</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>71660</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>66718</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>59733</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>58166</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>57330</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>59205</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>58036</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>56770</v>
       </c>
     </row>
@@ -886,60 +907,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>8410</v>
+      </c>
+      <c r="C8" t="n">
         <v>8481</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>8667</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>5383</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>5027</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>5496</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5824</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>6139</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5700</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>5893</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6029</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>5822</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>5929</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>6036</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>6050</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>5655</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>5404</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>3679</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>3901</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>3880</v>
       </c>
     </row>
@@ -953,25 +977,25 @@
         <v>20465</v>
       </c>
       <c r="C9" t="n">
-        <v>23912</v>
+        <v>20465</v>
       </c>
       <c r="D9" t="n">
         <v>23912</v>
       </c>
       <c r="E9" t="n">
+        <v>23912</v>
+      </c>
+      <c r="F9" t="n">
         <v>24693</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>24680</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>27442</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>27440</v>
-      </c>
-      <c r="I9" t="n">
-        <v>27591</v>
       </c>
       <c r="J9" t="n">
         <v>27591</v>
@@ -983,27 +1007,30 @@
         <v>27591</v>
       </c>
       <c r="M9" t="n">
+        <v>27591</v>
+      </c>
+      <c r="N9" t="n">
         <v>27587</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>27011</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>26786</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>26768</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>26971</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>26955</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>26943</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>26276</v>
       </c>
     </row>
@@ -1014,60 +1041,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>2545</v>
+      </c>
+      <c r="C10" t="n">
         <v>2722</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>2877</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>3057</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>3568</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>3975</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>4383</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>4675</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4970</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>5173</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>5567</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>6268</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>6427</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>6813</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>7684</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>8018</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>8408</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>9881</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>10303</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>10429</v>
       </c>
     </row>
@@ -1078,60 +1108,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>8065</v>
+      </c>
+      <c r="C11" t="n">
         <v>7049</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>12280</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>7283</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>7057</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>9006</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>14329</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>11947</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>13413</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>12671</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>12068</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>10134</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>8227</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>7210</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5452</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>5356</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>5327</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>6036</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6082</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>5911</v>
       </c>
     </row>
@@ -1142,253 +1175,265 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>202439</v>
+      </c>
+      <c r="C12" t="n">
         <v>205332</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>204514</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>192520</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>192242</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>193542</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>206205</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>192733</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>188837</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>185629</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>185303</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>174841</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>170418</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>176356</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>167962</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>154597</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>150622</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>145261</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>152539</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>147710</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Debt, Current</t>
+          <t>Accounts Payable, Current</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2004</v>
+        <v>8756</v>
       </c>
       <c r="C13" t="n">
-        <v>2496</v>
+        <v>7159</v>
       </c>
       <c r="D13" t="n">
-        <v>6731</v>
+        <v>10268</v>
       </c>
       <c r="E13" t="n">
-        <v>5240</v>
+        <v>10666</v>
       </c>
       <c r="F13" t="n">
-        <v>3765</v>
+        <v>10896</v>
       </c>
       <c r="G13" t="n">
-        <v>4695</v>
+        <v>11074</v>
       </c>
       <c r="H13" t="n">
-        <v>4581</v>
+        <v>9618</v>
       </c>
       <c r="I13" t="n">
-        <v>2288</v>
+        <v>8559</v>
       </c>
       <c r="J13" t="n">
-        <v>2711</v>
+        <v>8669</v>
       </c>
       <c r="K13" t="n">
-        <v>1437</v>
+        <v>8757</v>
       </c>
       <c r="L13" t="n">
-        <v>2283</v>
+        <v>8083</v>
       </c>
       <c r="M13" t="n">
-        <v>2882</v>
+        <v>7133</v>
       </c>
       <c r="N13" t="n">
-        <v>4459</v>
+        <v>7945</v>
       </c>
       <c r="O13" t="n">
-        <v>4694</v>
+        <v>7210</v>
       </c>
       <c r="P13" t="n">
-        <v>3695</v>
+        <v>6792</v>
       </c>
       <c r="Q13" t="n">
-        <v>2647</v>
+        <v>5917</v>
       </c>
       <c r="R13" t="n">
-        <v>504</v>
+        <v>5434</v>
       </c>
       <c r="S13" t="n">
-        <v>2254</v>
+        <v>5159</v>
       </c>
       <c r="T13" t="n">
-        <v>3464</v>
+        <v>5045</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4638</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Accounts Payable, Current</t>
+          <t>Employee-related Liabilities, Current</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7159</v>
+        <v>3748</v>
       </c>
       <c r="C14" t="n">
-        <v>10268</v>
+        <v>2824</v>
       </c>
       <c r="D14" t="n">
-        <v>10666</v>
+        <v>3756</v>
       </c>
       <c r="E14" t="n">
-        <v>10896</v>
+        <v>4249</v>
       </c>
       <c r="F14" t="n">
-        <v>11074</v>
+        <v>2652</v>
       </c>
       <c r="G14" t="n">
-        <v>9618</v>
+        <v>5015</v>
       </c>
       <c r="H14" t="n">
-        <v>8559</v>
+        <v>2651</v>
       </c>
       <c r="I14" t="n">
-        <v>8669</v>
+        <v>2506</v>
       </c>
       <c r="J14" t="n">
-        <v>8757</v>
+        <v>3115</v>
       </c>
       <c r="K14" t="n">
-        <v>8083</v>
+        <v>2887</v>
       </c>
       <c r="L14" t="n">
-        <v>7133</v>
+        <v>2497</v>
       </c>
       <c r="M14" t="n">
-        <v>7945</v>
+        <v>3421</v>
       </c>
       <c r="N14" t="n">
-        <v>7210</v>
+        <v>2730</v>
       </c>
       <c r="O14" t="n">
-        <v>6792</v>
+        <v>2731</v>
       </c>
       <c r="P14" t="n">
-        <v>5917</v>
+        <v>4026</v>
       </c>
       <c r="Q14" t="n">
-        <v>5434</v>
+        <v>3176</v>
       </c>
       <c r="R14" t="n">
-        <v>5159</v>
+        <v>2757</v>
       </c>
       <c r="S14" t="n">
-        <v>5045</v>
+        <v>3197</v>
       </c>
       <c r="T14" t="n">
-        <v>4638</v>
+        <v>2833</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2358</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Employee-related Liabilities, Current</t>
+          <t>Debt, Current</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2824</v>
+        <v>1988</v>
       </c>
       <c r="C15" t="n">
-        <v>3756</v>
+        <v>2004</v>
       </c>
       <c r="D15" t="n">
-        <v>4249</v>
+        <v>2496</v>
       </c>
       <c r="E15" t="n">
-        <v>2652</v>
+        <v>6731</v>
       </c>
       <c r="F15" t="n">
-        <v>5015</v>
+        <v>5240</v>
       </c>
       <c r="G15" t="n">
-        <v>2651</v>
+        <v>3765</v>
       </c>
       <c r="H15" t="n">
-        <v>2506</v>
+        <v>4695</v>
       </c>
       <c r="I15" t="n">
-        <v>3115</v>
+        <v>4581</v>
       </c>
       <c r="J15" t="n">
-        <v>2887</v>
+        <v>2288</v>
       </c>
       <c r="K15" t="n">
-        <v>2497</v>
+        <v>2711</v>
       </c>
       <c r="L15" t="n">
-        <v>3421</v>
+        <v>1437</v>
       </c>
       <c r="M15" t="n">
-        <v>2730</v>
+        <v>2283</v>
       </c>
       <c r="N15" t="n">
-        <v>2731</v>
+        <v>2882</v>
       </c>
       <c r="O15" t="n">
-        <v>4026</v>
+        <v>4459</v>
       </c>
       <c r="P15" t="n">
-        <v>3176</v>
+        <v>4694</v>
       </c>
       <c r="Q15" t="n">
-        <v>2757</v>
+        <v>3695</v>
       </c>
       <c r="R15" t="n">
-        <v>3197</v>
+        <v>2647</v>
       </c>
       <c r="S15" t="n">
-        <v>2833</v>
+        <v>504</v>
       </c>
       <c r="T15" t="n">
-        <v>2358</v>
+        <v>2254</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3464</v>
       </c>
     </row>
     <row r="16">
@@ -1398,60 +1443,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>21178</v>
+      </c>
+      <c r="C16" t="n">
         <v>14898</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>14952</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>12433</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>11513</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>12865</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>13207</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>11221</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>12430</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>10656</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>11330</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>14976</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>13661</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>14922</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>14060</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>12048</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>13313</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>13252</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>12349</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>13435</v>
       </c>
     </row>
@@ -1462,60 +1510,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>35670</v>
+      </c>
+      <c r="C17" t="n">
         <v>26885</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>32297</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>34966</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>32174</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>35159</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>32027</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>27213</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>28614</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>27180</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>27393</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>27813</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>27218</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>29322</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>29572</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>24836</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>24151</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>22112</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>22481</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>23895</v>
       </c>
     </row>
@@ -1526,60 +1577,63 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>48549</v>
+      </c>
+      <c r="C18" t="n">
         <v>43027</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>44057</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>44026</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>44911</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>46471</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>48334</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>47869</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>46591</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>46335</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>48836</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>37240</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>32548</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>32788</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>35610</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>31714</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>33237</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>36059</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>36093</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>36455</v>
       </c>
     </row>
@@ -1590,60 +1644,63 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>15077</v>
+      </c>
+      <c r="C19" t="n">
         <v>10431</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>11430</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>7777</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>8744</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>7048</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>5410</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>6895</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>7946</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>7643</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>4840</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>5760</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>5178</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>5191</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>5389</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>5329</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5322</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>3349</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>3108</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>2975</v>
       </c>
     </row>
@@ -1654,60 +1711,63 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>53780</v>
+      </c>
+      <c r="C20" t="n">
         <v>66259</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>56755</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>52334</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>51920</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>50665</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>49763</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>38291</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>35653</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>34330</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>32829</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>30912</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>29858</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>29244</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>27592</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>26655</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>26272</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>23335</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>25516</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>25251</v>
       </c>
     </row>
@@ -1718,60 +1778,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C21" t="n">
         <v>-44</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>19</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>65</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-486</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-185</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-696</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-542</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-861</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-544</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-419</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-2051</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-1625</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-1002</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-1147</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>-1095</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>-1103</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>-940</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>-1152</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-1541</v>
       </c>
     </row>
@@ -1782,60 +1845,63 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>33842</v>
+      </c>
+      <c r="C22" t="n">
         <v>45179</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>49602</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>45484</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>48322</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>49052</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>66162</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>68224</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>67021</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>67231</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>65649</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>71024</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>72985</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>74894</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>63642</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>59647</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>54638</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>52159</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>57646</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>52644</v>
       </c>
     </row>
@@ -1846,60 +1912,63 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>87542</v>
+      </c>
+      <c r="C23" t="n">
         <v>111394</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>106376</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>97883</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>99756</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>99532</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>115229</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>105973</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>101813</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>101017</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>98059</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>99885</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>101218</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>103136</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>90087</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>85207</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>79807</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>74554</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>82010</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>76354</v>
       </c>
     </row>
@@ -1910,11 +1979,11 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
         <v>5023</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
@@ -1964,6 +2033,9 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1977,35 +2049,35 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
         <v>825</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>887</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>1873</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>2440</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>1856</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>346</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>2112</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>2169</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>4046</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -2028,6 +2100,9 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2044,54 +2119,57 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>9643</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>8947</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>8785</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>11287</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>6923</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>7621</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>8349</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>8232</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>4529</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4390</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>6215</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>7870</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4746</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>5192</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>3356</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>8736</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>11380</v>
       </c>
     </row>
@@ -2129,33 +2207,36 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>3831</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>3782</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3684</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>4372</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>4223</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>4172</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>4605</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>4811</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4795</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>4651</v>
       </c>
     </row>
@@ -2196,30 +2277,33 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>56</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>32</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>236</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>6398</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>5817</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>5557</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2260,30 +2344,33 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>361</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>572</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>1547</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>3019</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3271</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>3410</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>2995</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>2723</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>2027</v>
       </c>
     </row>
@@ -2333,21 +2420,24 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>22761</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>17097</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>14788</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>11910</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>12288</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>8127</v>
       </c>
     </row>
@@ -2397,21 +2487,24 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>953</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>1262</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>1409</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>2720</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2884</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>2943</v>
       </c>
     </row>
@@ -2461,21 +2554,24 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>62</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>68</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>90</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>1381</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>1329</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>1353</v>
       </c>
     </row>
@@ -2490,65 +2586,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44835</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44744</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44653</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44464</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44100</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
     </row>
@@ -2559,60 +2658,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>16128</v>
+      </c>
+      <c r="C2" t="n">
         <v>13577</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>13653</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>12859</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>12667</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>13284</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>12833</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>12724</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>14158</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>12949</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>11715</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>15338</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>15321</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>18353</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>19192</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>19631</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>19673</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>18333</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>19728</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>19828</v>
       </c>
     </row>
@@ -2623,60 +2725,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>9619</v>
+      </c>
+      <c r="C3" t="n">
         <v>8230</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>8435</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>9317</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>7995</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>11287</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>8286</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>7507</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>8140</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>8311</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>7707</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>8803</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>9734</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>9109</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8446</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>8425</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>8819</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>8592</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>9221</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>7812</v>
       </c>
     </row>
@@ -2687,60 +2792,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>6509</v>
+      </c>
+      <c r="C4" t="n">
         <v>5347</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>5218</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>3542</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>4672</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1997</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4547</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5217</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>6018</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>4638</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4008</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>6535</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>5587</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>9244</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>10746</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>11206</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>10854</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>9741</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>10507</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>12016</v>
       </c>
     </row>
@@ -2751,60 +2859,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C5" t="n">
         <v>3375</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>3231</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>3684</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3640</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>4049</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4239</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4382</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>3870</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>4080</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4109</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>4302</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>4400</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>4362</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3803</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3715</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>3623</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>3272</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>3354</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>3275</v>
       </c>
     </row>
@@ -2815,60 +2926,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1175</v>
+      </c>
+      <c r="C6" t="n">
         <v>1038</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1129</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>1144</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1177</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1383</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1329</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1556</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1340</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1374</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>1303</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1744</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1800</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>1752</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1674</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>1599</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>1328</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>1435</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1447</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1541</v>
       </c>
     </row>
@@ -2879,60 +2993,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>170</v>
+      </c>
+      <c r="C7" t="n">
         <v>4070</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>175</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1890</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>156</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>5622</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>943</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>348</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>816</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>200</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>64</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>664</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>87</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-1211</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>42</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>346</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>2209</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>-25</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>9</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>162</v>
       </c>
     </row>
@@ -2943,60 +3060,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4713</v>
+      </c>
+      <c r="C8" t="n">
         <v>8483</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>4535</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>6718</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>4973</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>11054</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>6511</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>6286</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6026</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>5654</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>5476</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>6710</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>6287</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>4903</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>5519</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>5660</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>7160</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>4682</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>4810</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>4978</v>
       </c>
     </row>
@@ -3007,125 +3127,131 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1796</v>
+      </c>
+      <c r="C9" t="n">
         <v>-3136</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>683</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-3176</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-301</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-9057</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-1964</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>-1069</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-8</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-1016</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-1468</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-175</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-700</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>4341</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>5227</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>5546</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>3694</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>5059</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>5697</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>7038</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Equity Securities, FV-NI, Gain (Loss)</t>
+          <t>intc_GainsLossesOnEquityInvestments</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-72</v>
+        <v>-39</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-112</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-159</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-191</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4323</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1707</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-111</v>
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3135,60 +3261,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-12576</v>
+      </c>
+      <c r="C11" t="n">
         <v>-738</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>3670</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-95</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-173</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>130</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>80</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>145</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>147</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>224</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>141</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>138</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-119</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>997</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>-76</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>-96</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>-156</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>-74</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-29</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-313</v>
       </c>
     </row>
@@ -3199,60 +3328,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-10819</v>
+      </c>
+      <c r="C12" t="n">
         <v>-3946</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>4574</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-2769</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-586</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-9086</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-2004</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-719</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-52</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-816</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-1158</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-188</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-909</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>9661</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6858</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>5745</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>3906</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>5041</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>5935</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>6614</v>
       </c>
     </row>
@@ -3263,60 +3395,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>29</v>
+      </c>
+      <c r="C13" t="n">
         <v>335</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>304</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>255</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>301</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>7903</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-350</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-282</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-362</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-2289</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1610</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-1207</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-455</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1548</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>35</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>684</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>545</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>765</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>830</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>953</v>
       </c>
     </row>
@@ -3327,60 +3462,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>-11033</v>
+      </c>
+      <c r="C14" t="n">
         <v>-3728</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>4063</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>-2918</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>-821</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-16639</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>-1610</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>-381</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>297</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1481</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>-2758</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1019</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-454</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>8113</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>6823</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>5061</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>3361</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>4276</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>5105</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>5661</v>
       </c>
     </row>
@@ -3391,60 +3529,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="C15" t="n">
         <v>-0.73</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>0.9</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-0.67</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-0.19</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-3.88</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>-0.38</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-0.09</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>0.35</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-0.66</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.25</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>-0.11</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>1.99</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.68</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>0.83</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>1.02</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>1.2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>1.33</v>
       </c>
     </row>
@@ -3455,188 +3596,264 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>5104</v>
+      </c>
+      <c r="C16" t="n">
         <v>5083</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>4514</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>4369</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>4343</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>4292</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4267</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>4242</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>4202</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>4182</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>4154</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>4118</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>4100</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>4079</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>4061</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>4049</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>4056</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>4188</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>4246</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>4266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Diluted</t>
+          <t>Equity Securities, FV-NI, Gain (Loss)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5083</v>
+        <v>-39</v>
       </c>
       <c r="C17" t="n">
-        <v>4531</v>
+        <v>-72</v>
       </c>
       <c r="D17" t="n">
-        <v>4369</v>
+        <v>221</v>
       </c>
       <c r="E17" t="n">
-        <v>4343</v>
+        <v>502</v>
       </c>
       <c r="F17" t="n">
-        <v>4292</v>
+        <v>-112</v>
       </c>
       <c r="G17" t="n">
-        <v>4267</v>
+        <v>-159</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="I17" t="n">
-        <v>4229</v>
+        <v>205</v>
       </c>
       <c r="J17" t="n">
-        <v>4196</v>
+        <v>-191</v>
       </c>
       <c r="K17" t="n">
-        <v>4154</v>
+        <v>-24</v>
       </c>
       <c r="L17" t="n">
-        <v>4125</v>
+        <v>169</v>
       </c>
       <c r="M17" t="n">
-        <v>4100</v>
+        <v>-151</v>
       </c>
       <c r="N17" t="n">
-        <v>4107</v>
+        <v>-90</v>
       </c>
       <c r="O17" t="n">
-        <v>4086</v>
+        <v>4323</v>
       </c>
       <c r="P17" t="n">
-        <v>4084</v>
+        <v>1707</v>
       </c>
       <c r="Q17" t="n">
-        <v>4096</v>
+        <v>295</v>
       </c>
       <c r="R17" t="n">
-        <v>4211</v>
+        <v>368</v>
       </c>
       <c r="S17" t="n">
-        <v>4284</v>
+        <v>56</v>
       </c>
       <c r="T17" t="n">
-        <v>4312</v>
+        <v>267</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Number of Shares - Diluted</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5104</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5083</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4531</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4369</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4343</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4292</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4267</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4229</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4196</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4154</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4125</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4100</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4107</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4086</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4084</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4211</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4284</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="C19" t="n">
         <v>-0.73</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D19" t="n">
         <v>0.9</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E19" t="n">
         <v>-0.67</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F19" t="n">
         <v>-0.19</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G19" t="n">
         <v>-3.88</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H19" t="n">
         <v>-0.38</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I19" t="n">
         <v>-0.09</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K19" t="n">
         <v>0.35</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L19" t="n">
         <v>-0.66</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M19" t="n">
         <v>0.25</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N19" t="n">
         <v>-0.11</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O19" t="n">
         <v>1.98</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P19" t="n">
         <v>1.67</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q19" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R19" t="n">
         <v>0.82</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S19" t="n">
         <v>1.02</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T19" t="n">
         <v>1.19</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U19" t="n">
         <v>1.31</v>
       </c>
     </row>
@@ -3651,65 +3868,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T55"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44835</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44744</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44653</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44464</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44100</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
     </row>
@@ -3720,60 +3940,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>-15129</v>
+      </c>
+      <c r="C2" t="n">
         <v>-4281</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>359</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>-3911</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-887</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>-19080</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>-2091</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>-437</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>-985</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-1295</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-2768</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>8678</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7659</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>8113</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>15245</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>8422</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>3361</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>15042</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>10766</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>5661</v>
       </c>
     </row>
@@ -3784,60 +4007,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5891</v>
+      </c>
+      <c r="C3" t="n">
         <v>2902</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>7971</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5213</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2425</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>7651</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4403</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2200</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5753</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>3733</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1901</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>8309</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>5528</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2847</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>7357</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>4862</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2454</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>7925</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>5248</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2623</v>
       </c>
     </row>
@@ -3848,60 +4074,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1307</v>
+      </c>
+      <c r="C4" t="n">
         <v>621</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1896</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1348</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>684</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>2759</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1959</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1179</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2433</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1661</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>739</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2392</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1599</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>707</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1587</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1044</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>425</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1393</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>941</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>449</v>
       </c>
     </row>
@@ -3912,60 +4141,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3967</v>
+      </c>
+      <c r="C5" t="n">
         <v>3965</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>372</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>382</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>3626</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1291</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>348</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>718</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>255</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>55</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>665</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>73</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>17</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>2597</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>2555</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2209</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3976,60 +4208,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>469</v>
+      </c>
+      <c r="C6" t="n">
         <v>234</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>708</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>474</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>249</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1081</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>717</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>351</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1336</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>909</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>465</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1439</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>968</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>501</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1361</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>897</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>448</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>1311</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>865</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>427</v>
       </c>
     </row>
@@ -4040,60 +4275,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>111</v>
+      </c>
+      <c r="C7" t="n">
         <v>72</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>-611</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>-390</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>112</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>75</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-84</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-208</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>47</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-146</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-167</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>-4075</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>-4230</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-4325</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-1113</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-555</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-299</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>-105</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>-92</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>134</v>
       </c>
     </row>
@@ -4104,14 +4342,14 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>13619</v>
+      </c>
+      <c r="C8" t="n">
         <v>1090</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1687</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
@@ -4158,29 +4396,32 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Expense (Benefit)</t>
+          <t>Deferred Income Taxes and Tax Credits</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9</v>
+        <v>-27</v>
       </c>
       <c r="C9" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6368</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4222,678 +4463,711 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accounts Receivable</t>
+          <t>Asset Impairment Charges And Gain Loss On Disposal Of Property Plant And Equipment</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-217</v>
+        <v>165</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1004</v>
+        <v>465</v>
       </c>
       <c r="E10" t="n">
-        <v>414</v>
+        <v>482</v>
       </c>
       <c r="F10" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>272</v>
+        <v>2290</v>
       </c>
       <c r="H10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1137</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1991</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3397</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2384</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-1618</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-678</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-426</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-796</v>
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Inventories</t>
+          <t>Increase (Decrease) in Accounts Receivable</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-808</v>
+        <v>-221</v>
       </c>
       <c r="C11" t="n">
-        <v>-9</v>
+        <v>-217</v>
       </c>
       <c r="D11" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="E11" t="n">
-        <v>-83</v>
+        <v>1004</v>
       </c>
       <c r="F11" t="n">
-        <v>-969</v>
+        <v>414</v>
       </c>
       <c r="G11" t="n">
-        <v>-116</v>
+        <v>282</v>
       </c>
       <c r="H11" t="n">
-        <v>-366</v>
+        <v>272</v>
       </c>
       <c r="I11" t="n">
-        <v>1758</v>
+        <v>80</v>
       </c>
       <c r="J11" t="n">
-        <v>1240</v>
+        <v>1290</v>
       </c>
       <c r="K11" t="n">
-        <v>231</v>
+        <v>1137</v>
       </c>
       <c r="L11" t="n">
-        <v>-2043</v>
+        <v>286</v>
       </c>
       <c r="M11" t="n">
-        <v>-1386</v>
+        <v>1991</v>
       </c>
       <c r="N11" t="n">
-        <v>-1147</v>
+        <v>3397</v>
       </c>
       <c r="O11" t="n">
-        <v>-1212</v>
+        <v>2384</v>
       </c>
       <c r="P11" t="n">
-        <v>-126</v>
+        <v>-1618</v>
       </c>
       <c r="Q11" t="n">
-        <v>180</v>
+        <v>-678</v>
       </c>
       <c r="R11" t="n">
-        <v>-570</v>
+        <v>-426</v>
       </c>
       <c r="S11" t="n">
-        <v>-271</v>
+        <v>525</v>
       </c>
       <c r="T11" t="n">
-        <v>-548</v>
+        <v>224</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-796</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accounts Payable</t>
+          <t>Increase (Decrease) in Inventories</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-142</v>
+        <v>-874</v>
       </c>
       <c r="C12" t="n">
-        <v>-281</v>
+        <v>-808</v>
       </c>
       <c r="D12" t="n">
-        <v>114</v>
+        <v>-9</v>
       </c>
       <c r="E12" t="n">
-        <v>-240</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>566</v>
+        <v>-83</v>
       </c>
       <c r="G12" t="n">
-        <v>184</v>
+        <v>-969</v>
       </c>
       <c r="H12" t="n">
-        <v>-386</v>
+        <v>-116</v>
       </c>
       <c r="I12" t="n">
-        <v>-1082</v>
+        <v>-366</v>
       </c>
       <c r="J12" t="n">
-        <v>-1102</v>
+        <v>1758</v>
       </c>
       <c r="K12" t="n">
-        <v>-771</v>
+        <v>1240</v>
       </c>
       <c r="L12" t="n">
-        <v>-485</v>
+        <v>231</v>
       </c>
       <c r="M12" t="n">
-        <v>117</v>
+        <v>-2043</v>
       </c>
       <c r="N12" t="n">
-        <v>-128</v>
+        <v>-1386</v>
       </c>
       <c r="O12" t="n">
-        <v>1095</v>
+        <v>-1147</v>
       </c>
       <c r="P12" t="n">
-        <v>425</v>
+        <v>-1212</v>
       </c>
       <c r="Q12" t="n">
-        <v>303</v>
+        <v>-126</v>
       </c>
       <c r="R12" t="n">
-        <v>355</v>
+        <v>180</v>
       </c>
       <c r="S12" t="n">
-        <v>208</v>
+        <v>-570</v>
       </c>
       <c r="T12" t="n">
-        <v>117</v>
+        <v>-271</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-548</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Employee Related Liabilities</t>
+          <t>Increase (Decrease) in Accounts Payable</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1175</v>
+        <v>310</v>
       </c>
       <c r="C13" t="n">
-        <v>541</v>
+        <v>-142</v>
       </c>
       <c r="D13" t="n">
-        <v>1022</v>
+        <v>-281</v>
       </c>
       <c r="E13" t="n">
-        <v>-741</v>
+        <v>114</v>
       </c>
       <c r="F13" t="n">
-        <v>1384</v>
+        <v>-240</v>
       </c>
       <c r="G13" t="n">
-        <v>-1309</v>
+        <v>566</v>
       </c>
       <c r="H13" t="n">
-        <v>-1289</v>
+        <v>184</v>
       </c>
       <c r="I13" t="n">
-        <v>-1171</v>
+        <v>-386</v>
       </c>
       <c r="J13" t="n">
-        <v>-1340</v>
+        <v>-1082</v>
       </c>
       <c r="K13" t="n">
-        <v>-1560</v>
+        <v>-1102</v>
       </c>
       <c r="L13" t="n">
-        <v>-1912</v>
+        <v>-771</v>
       </c>
       <c r="M13" t="n">
-        <v>-1985</v>
+        <v>-485</v>
       </c>
       <c r="N13" t="n">
-        <v>-1884</v>
+        <v>117</v>
       </c>
       <c r="O13" t="n">
-        <v>-16</v>
+        <v>-128</v>
       </c>
       <c r="P13" t="n">
-        <v>-836</v>
+        <v>1095</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1283</v>
+        <v>425</v>
       </c>
       <c r="R13" t="n">
-        <v>-488</v>
+        <v>303</v>
       </c>
       <c r="S13" t="n">
-        <v>-919</v>
+        <v>355</v>
       </c>
       <c r="T13" t="n">
-        <v>-1500</v>
+        <v>208</v>
+      </c>
+      <c r="U13" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Income Taxes Payable, Net of Income Taxes Receivable</t>
+          <t>Increase (Decrease) in Employee Related Liabilities</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>169</v>
+        <v>-372</v>
       </c>
       <c r="C14" t="n">
-        <v>-1196</v>
+        <v>-1175</v>
       </c>
       <c r="D14" t="n">
-        <v>-1338</v>
+        <v>541</v>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>1022</v>
       </c>
       <c r="F14" t="n">
-        <v>-930</v>
+        <v>-741</v>
       </c>
       <c r="G14" t="n">
-        <v>-2174</v>
+        <v>1384</v>
       </c>
       <c r="H14" t="n">
-        <v>-591</v>
+        <v>-1309</v>
       </c>
       <c r="I14" t="n">
-        <v>-2676</v>
+        <v>-1289</v>
       </c>
       <c r="J14" t="n">
-        <v>-2186</v>
+        <v>-1171</v>
       </c>
       <c r="K14" t="n">
-        <v>1344</v>
+        <v>-1340</v>
       </c>
       <c r="L14" t="n">
-        <v>-4062</v>
+        <v>-1560</v>
       </c>
       <c r="M14" t="n">
-        <v>-2232</v>
+        <v>-1912</v>
       </c>
       <c r="N14" t="n">
-        <v>1219</v>
+        <v>-1985</v>
       </c>
       <c r="O14" t="n">
-        <v>-570</v>
+        <v>-1884</v>
       </c>
       <c r="P14" t="n">
-        <v>114</v>
+        <v>-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>383</v>
+        <v>-836</v>
       </c>
       <c r="R14" t="n">
-        <v>493</v>
+        <v>-1283</v>
       </c>
       <c r="S14" t="n">
-        <v>1203</v>
+        <v>-488</v>
       </c>
       <c r="T14" t="n">
-        <v>753</v>
+        <v>-919</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Other Operating Assets and Liabilities, Net</t>
+          <t>Increase (Decrease) in Income Taxes Payable, Net of Income Taxes Receivable</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1325</v>
+        <v>-477</v>
       </c>
       <c r="C15" t="n">
-        <v>-1423</v>
+        <v>169</v>
       </c>
       <c r="D15" t="n">
-        <v>-1742</v>
+        <v>-1196</v>
       </c>
       <c r="E15" t="n">
-        <v>-1206</v>
+        <v>-1338</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G15" t="n">
-        <v>-1983</v>
+        <v>-930</v>
       </c>
       <c r="H15" t="n">
-        <v>-2104</v>
+        <v>-2174</v>
       </c>
       <c r="I15" t="n">
-        <v>-574</v>
+        <v>-591</v>
       </c>
       <c r="J15" t="n">
-        <v>-1843</v>
+        <v>-2676</v>
       </c>
       <c r="K15" t="n">
-        <v>-1540</v>
+        <v>-2186</v>
       </c>
       <c r="L15" t="n">
-        <v>-2077</v>
+        <v>1344</v>
       </c>
       <c r="M15" t="n">
-        <v>-1724</v>
+        <v>-4062</v>
       </c>
       <c r="N15" t="n">
-        <v>-1286</v>
+        <v>-2232</v>
       </c>
       <c r="O15" t="n">
-        <v>1058</v>
+        <v>1219</v>
       </c>
       <c r="P15" t="n">
-        <v>-259</v>
+        <v>-570</v>
       </c>
       <c r="Q15" t="n">
-        <v>-641</v>
+        <v>114</v>
       </c>
       <c r="R15" t="n">
-        <v>-296</v>
+        <v>383</v>
       </c>
       <c r="S15" t="n">
-        <v>-697</v>
+        <v>493</v>
       </c>
       <c r="T15" t="n">
-        <v>-1075</v>
+        <v>1203</v>
+      </c>
+      <c r="U15" t="n">
+        <v>753</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Adjustments to Reconcile Net Income (Loss) to Cash Provided by (Used in) Operating Activities</t>
+          <t>Increase (Decrease) in Other Operating Assets and Liabilities, Net</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5377</v>
+        <v>-637</v>
       </c>
       <c r="C16" t="n">
-        <v>5050</v>
+        <v>-1325</v>
       </c>
       <c r="D16" t="n">
-        <v>6774</v>
+        <v>-1423</v>
       </c>
       <c r="E16" t="n">
-        <v>1700</v>
+        <v>-1742</v>
       </c>
       <c r="F16" t="n">
-        <v>24203</v>
+        <v>-1206</v>
       </c>
       <c r="G16" t="n">
-        <v>3160</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>-786</v>
+        <v>-1983</v>
       </c>
       <c r="I16" t="n">
-        <v>7832</v>
+        <v>-2104</v>
       </c>
       <c r="J16" t="n">
-        <v>2318</v>
+        <v>-574</v>
       </c>
       <c r="K16" t="n">
-        <v>983</v>
+        <v>-1843</v>
       </c>
       <c r="L16" t="n">
-        <v>-948</v>
+        <v>-1540</v>
       </c>
       <c r="M16" t="n">
-        <v>-959</v>
+        <v>-2077</v>
       </c>
       <c r="N16" t="n">
-        <v>-2222</v>
+        <v>-1724</v>
       </c>
       <c r="O16" t="n">
-        <v>8949</v>
+        <v>-1286</v>
       </c>
       <c r="P16" t="n">
-        <v>5872</v>
+        <v>1058</v>
       </c>
       <c r="Q16" t="n">
-        <v>2187</v>
+        <v>-259</v>
       </c>
       <c r="R16" t="n">
-        <v>10452</v>
+        <v>-641</v>
       </c>
       <c r="S16" t="n">
-        <v>6549</v>
+        <v>-296</v>
       </c>
       <c r="T16" t="n">
-        <v>497</v>
+        <v>-697</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1075</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Operating Activities</t>
+          <t>Adjustments to Reconcile Net Income (Loss) to Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1096</v>
+        <v>23231</v>
       </c>
       <c r="C17" t="n">
-        <v>5409</v>
+        <v>5377</v>
       </c>
       <c r="D17" t="n">
-        <v>2863</v>
+        <v>5050</v>
       </c>
       <c r="E17" t="n">
-        <v>813</v>
+        <v>6774</v>
       </c>
       <c r="F17" t="n">
-        <v>5123</v>
+        <v>1700</v>
       </c>
       <c r="G17" t="n">
-        <v>1069</v>
+        <v>24203</v>
       </c>
       <c r="H17" t="n">
-        <v>-1223</v>
+        <v>3160</v>
       </c>
       <c r="I17" t="n">
-        <v>6847</v>
+        <v>-786</v>
       </c>
       <c r="J17" t="n">
-        <v>1023</v>
+        <v>7832</v>
       </c>
       <c r="K17" t="n">
-        <v>-1785</v>
+        <v>2318</v>
       </c>
       <c r="L17" t="n">
-        <v>7730</v>
+        <v>983</v>
       </c>
       <c r="M17" t="n">
-        <v>6700</v>
+        <v>-948</v>
       </c>
       <c r="N17" t="n">
-        <v>5891</v>
+        <v>-959</v>
       </c>
       <c r="O17" t="n">
-        <v>24194</v>
+        <v>-2222</v>
       </c>
       <c r="P17" t="n">
-        <v>14294</v>
+        <v>8949</v>
       </c>
       <c r="Q17" t="n">
-        <v>5548</v>
+        <v>5872</v>
       </c>
       <c r="R17" t="n">
-        <v>25494</v>
+        <v>2187</v>
       </c>
       <c r="S17" t="n">
-        <v>17315</v>
+        <v>10452</v>
       </c>
       <c r="T17" t="n">
-        <v>6158</v>
+        <v>6549</v>
+      </c>
+      <c r="U17" t="n">
+        <v>497</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Purchases Of Property And Equipment And Intangible Assets</t>
+          <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-3636</v>
+        <v>8102</v>
       </c>
       <c r="C18" t="n">
-        <v>-11158</v>
+        <v>1096</v>
       </c>
       <c r="D18" t="n">
-        <v>-8733</v>
+        <v>5409</v>
       </c>
       <c r="E18" t="n">
-        <v>-5183</v>
+        <v>2863</v>
       </c>
       <c r="F18" t="n">
-        <v>-18110</v>
+        <v>813</v>
       </c>
       <c r="G18" t="n">
-        <v>-11652</v>
+        <v>5123</v>
       </c>
       <c r="H18" t="n">
-        <v>-5970</v>
+        <v>1069</v>
       </c>
       <c r="I18" t="n">
-        <v>-19054</v>
+        <v>-1223</v>
       </c>
       <c r="J18" t="n">
-        <v>-13301</v>
+        <v>6847</v>
       </c>
       <c r="K18" t="n">
-        <v>-7413</v>
+        <v>1023</v>
       </c>
       <c r="L18" t="n">
-        <v>-19145</v>
+        <v>-1785</v>
       </c>
       <c r="M18" t="n">
-        <v>-11846</v>
+        <v>7730</v>
       </c>
       <c r="N18" t="n">
-        <v>-4604</v>
+        <v>6700</v>
       </c>
       <c r="O18" t="n">
-        <v>-11579</v>
+        <v>5891</v>
       </c>
       <c r="P18" t="n">
-        <v>-7574</v>
+        <v>24194</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3972</v>
+        <v>14294</v>
       </c>
       <c r="R18" t="n">
-        <v>-10392</v>
+        <v>5548</v>
       </c>
       <c r="S18" t="n">
-        <v>-6676</v>
+        <v>25494</v>
       </c>
       <c r="T18" t="n">
-        <v>-3268</v>
+        <v>17315</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Proceeds From Capital Grants</t>
+          <t>Purchases Of Property And Equipment And Intangible Assets</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>107</v>
+        <v>-6192</v>
       </c>
       <c r="C19" t="n">
-        <v>1018</v>
+        <v>-3636</v>
       </c>
       <c r="D19" t="n">
-        <v>964</v>
+        <v>-11158</v>
       </c>
       <c r="E19" t="n">
-        <v>803</v>
+        <v>-8733</v>
       </c>
       <c r="F19" t="n">
-        <v>725</v>
+        <v>-5183</v>
       </c>
       <c r="G19" t="n">
-        <v>699</v>
+        <v>-18110</v>
       </c>
       <c r="H19" t="n">
-        <v>592</v>
+        <v>-11652</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-5970</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-19054</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-13301</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-7413</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-19145</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-11846</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-4604</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-11579</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-7574</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-3972</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-10392</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-6676</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-3268</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Businesses, Net of Cash Acquired</t>
+          <t>Proceeds From Capital Grants</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-596</v>
+        <v>167</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>964</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -4926,181 +5200,190 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Debt Securities, Available-for-sale</t>
+          <t>Payments to Acquire Businesses, Net of Cash Acquired</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-7190</v>
+        <v>-596</v>
       </c>
       <c r="C21" t="n">
-        <v>-16401</v>
+        <v>-596</v>
       </c>
       <c r="D21" t="n">
-        <v>-5730</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-3386</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-31519</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-17634</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-6460</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-37287</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-25696</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-16132</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-31669</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-25514</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-19091</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-3983</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-593</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-6323</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-4558</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-513</v>
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
+          <t>Payments to Acquire Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9221</v>
+        <v>-12737</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-7190</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-16401</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-5730</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-3386</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-31519</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-17634</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-6460</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-37287</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-25696</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-16132</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-31669</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-25514</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-19091</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-3983</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-593</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-6323</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-4558</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-513</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Maturities, Prepayments and Calls of Debt Securities, Available-for-sale</t>
+          <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5227</v>
+        <v>11009</v>
       </c>
       <c r="C23" t="n">
-        <v>10964</v>
+        <v>9221</v>
       </c>
       <c r="D23" t="n">
-        <v>8575</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>5327</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>34268</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>17214</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>9598</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>36725</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>26957</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>14173</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>35129</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>25407</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10490</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5118,56 +5401,59 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Divestiture of Businesses</t>
+          <t>Proceeds from Maturities, Prepayments and Calls of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>7724</v>
       </c>
       <c r="C24" t="n">
-        <v>6186</v>
+        <v>5227</v>
       </c>
       <c r="D24" t="n">
-        <v>1935</v>
+        <v>10964</v>
       </c>
       <c r="E24" t="n">
-        <v>1935</v>
+        <v>8575</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5327</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>34268</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>17214</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>9598</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>36725</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>26957</v>
       </c>
       <c r="L24" t="n">
-        <v>6579</v>
+        <v>14173</v>
       </c>
       <c r="M24" t="n">
-        <v>6579</v>
+        <v>35129</v>
       </c>
       <c r="N24" t="n">
-        <v>6544</v>
+        <v>25407</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>10490</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -5182,233 +5468,245 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Payments for (Proceeds from) Other Investing Activities</t>
+          <t>Proceeds from Divestiture of Businesses</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>984</v>
+        <v>6186</v>
       </c>
       <c r="E25" t="n">
-        <v>585</v>
+        <v>1935</v>
       </c>
       <c r="F25" t="n">
-        <v>144</v>
+        <v>1935</v>
       </c>
       <c r="G25" t="n">
-        <v>-355</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-323</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-2614</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1667</v>
+        <v>6579</v>
       </c>
       <c r="N25" t="n">
-        <v>-468</v>
+        <v>6579</v>
       </c>
       <c r="O25" t="n">
-        <v>620</v>
+        <v>6544</v>
       </c>
       <c r="P25" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-256</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-602</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-363</v>
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Investing Activities</t>
+          <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3093</v>
+        <v>-44</v>
       </c>
       <c r="C26" t="n">
-        <v>-8255</v>
+        <v>-40</v>
       </c>
       <c r="D26" t="n">
-        <v>-2005</v>
+        <v>494</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>984</v>
       </c>
       <c r="F26" t="n">
-        <v>-14492</v>
+        <v>585</v>
       </c>
       <c r="G26" t="n">
-        <v>-11728</v>
+        <v>144</v>
       </c>
       <c r="H26" t="n">
-        <v>-2563</v>
+        <v>-355</v>
       </c>
       <c r="I26" t="n">
-        <v>-18723</v>
+        <v>-323</v>
       </c>
       <c r="J26" t="n">
-        <v>-11329</v>
+        <v>518</v>
       </c>
       <c r="K26" t="n">
-        <v>-8521</v>
+        <v>458</v>
       </c>
       <c r="L26" t="n">
-        <v>-7046</v>
+        <v>735</v>
       </c>
       <c r="M26" t="n">
-        <v>-2472</v>
+        <v>-2614</v>
       </c>
       <c r="N26" t="n">
-        <v>-2640</v>
+        <v>-1667</v>
       </c>
       <c r="O26" t="n">
-        <v>-20133</v>
+        <v>-468</v>
       </c>
       <c r="P26" t="n">
-        <v>-9451</v>
+        <v>620</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2547</v>
+        <v>380</v>
       </c>
       <c r="R26" t="n">
-        <v>-15112</v>
+        <v>406</v>
       </c>
       <c r="S26" t="n">
-        <v>-14346</v>
+        <v>-256</v>
       </c>
       <c r="T26" t="n">
-        <v>-3736</v>
+        <v>-602</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-363</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Commercial Paper</t>
+          <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-669</v>
       </c>
       <c r="C27" t="n">
-        <v>3493</v>
+        <v>3093</v>
       </c>
       <c r="D27" t="n">
-        <v>3493</v>
+        <v>-8255</v>
       </c>
       <c r="E27" t="n">
-        <v>1496</v>
+        <v>-2005</v>
       </c>
       <c r="F27" t="n">
-        <v>7349</v>
+        <v>81</v>
       </c>
       <c r="G27" t="n">
-        <v>5804</v>
+        <v>-14492</v>
       </c>
       <c r="H27" t="n">
-        <v>793</v>
+        <v>-11728</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-2563</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-18723</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>-11329</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>-8521</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>-7046</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>-2472</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>-2640</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-20133</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-9451</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>-2547</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-15112</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>-14346</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-3736</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Proceeds From Partner Contributions</t>
+          <t>Proceeds from Issuance of Commercial Paper</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2064</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3652</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2238</v>
+        <v>3493</v>
       </c>
       <c r="E28" t="n">
-        <v>955</v>
+        <v>3493</v>
       </c>
       <c r="F28" t="n">
-        <v>12278</v>
+        <v>1496</v>
       </c>
       <c r="G28" t="n">
-        <v>11861</v>
+        <v>7349</v>
       </c>
       <c r="H28" t="n">
-        <v>423</v>
+        <v>5804</v>
       </c>
       <c r="I28" t="n">
-        <v>1106</v>
+        <v>793</v>
       </c>
       <c r="J28" t="n">
-        <v>834</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -5438,47 +5736,50 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Payments To Acquire Property Plant And Equipment Financing Activities</t>
+          <t>Repayments of Commercial Paper</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1327</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-2493</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-1962</v>
+        <v>-3493</v>
       </c>
       <c r="E29" t="n">
-        <v>-1020</v>
+        <v>-1496</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-7349</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-2609</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-3944</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>-3944</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-2930</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -5502,422 +5803,443 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Long-term Debt</t>
+          <t>Finance Lease, Principal Payments</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1500</v>
+        <v>-832</v>
       </c>
       <c r="C30" t="n">
-        <v>-3750</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-2288</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-2288</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>-423</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="L30" t="n">
-        <v>-3088</v>
+        <v>-15</v>
       </c>
       <c r="M30" t="n">
-        <v>-1688</v>
+        <v>-341</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>-299</v>
       </c>
       <c r="O30" t="n">
-        <v>-500</v>
+        <v>-299</v>
       </c>
       <c r="P30" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-4525</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>-2775</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-1075</v>
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Stock Plans</t>
+          <t>Proceeds from Noncontrolling Interests</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>427</v>
+        <v>4082</v>
       </c>
       <c r="C31" t="n">
-        <v>777</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>491</v>
+        <v>922</v>
       </c>
       <c r="E31" t="n">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>986</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>631</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2423</v>
       </c>
       <c r="K31" t="n">
-        <v>659</v>
+        <v>1573</v>
       </c>
       <c r="L31" t="n">
-        <v>972</v>
+        <v>449</v>
       </c>
       <c r="M31" t="n">
-        <v>589</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>589</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>589</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>897</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>503</v>
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments for) Other Financing Activities</t>
+          <t>Payments to Noncontrolling Interests</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-870</v>
+        <v>-14339</v>
       </c>
       <c r="C32" t="n">
-        <v>-1052</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-678</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>-618</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-1277</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-444</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-220</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>-225</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-281</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-666</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-815</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>-527</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>629</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>726</v>
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Payments To Acquire Property Plant And Equipment Financing Activities</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1206</v>
+        <v>-1423</v>
       </c>
       <c r="C33" t="n">
-        <v>5738</v>
+        <v>-1327</v>
       </c>
       <c r="D33" t="n">
-        <v>586</v>
+        <v>-2493</v>
       </c>
       <c r="E33" t="n">
-        <v>-196</v>
+        <v>-1962</v>
       </c>
       <c r="F33" t="n">
-        <v>11075</v>
+        <v>-1020</v>
       </c>
       <c r="G33" t="n">
-        <v>14867</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>8353</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>7511</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>7394</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>-982</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-4665</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>-1863</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>-2056</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-5962</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>-3674</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-11220</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1573</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>4764</v>
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Proceeds from Issuance of Long-term Debt</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2983</v>
+        <v>13000</v>
       </c>
       <c r="C34" t="n">
-        <v>2892</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1444</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1706</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4208</v>
+        <v>2975</v>
       </c>
       <c r="H34" t="n">
-        <v>-156</v>
+        <v>2975</v>
       </c>
       <c r="I34" t="n">
-        <v>-3523</v>
+        <v>2537</v>
       </c>
       <c r="J34" t="n">
-        <v>-2795</v>
+        <v>11391</v>
       </c>
       <c r="K34" t="n">
-        <v>-2912</v>
+        <v>10968</v>
       </c>
       <c r="L34" t="n">
-        <v>-298</v>
+        <v>10968</v>
       </c>
       <c r="M34" t="n">
-        <v>-437</v>
+        <v>6103</v>
       </c>
       <c r="N34" t="n">
-        <v>1388</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2005</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-1119</v>
+        <v>4974</v>
       </c>
       <c r="Q34" t="n">
-        <v>-673</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>-838</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>4542</v>
+        <v>10247</v>
       </c>
       <c r="T34" t="n">
-        <v>7186</v>
+        <v>10247</v>
+      </c>
+      <c r="U34" t="n">
+        <v>10247</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Capital Expenditures Incurred but Not yet Paid</t>
+          <t>Repayments of Long-term Debt</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1949</v>
+        <v>-9000</v>
       </c>
       <c r="C35" t="n">
-        <v>5068</v>
+        <v>-1500</v>
       </c>
       <c r="D35" t="n">
-        <v>5155</v>
+        <v>-3750</v>
       </c>
       <c r="E35" t="n">
-        <v>3932</v>
+        <v>-1500</v>
       </c>
       <c r="F35" t="n">
-        <v>6595</v>
+        <v>-1500</v>
       </c>
       <c r="G35" t="n">
-        <v>5544</v>
+        <v>-2288</v>
       </c>
       <c r="H35" t="n">
-        <v>5167</v>
+        <v>-2288</v>
       </c>
       <c r="I35" t="n">
-        <v>5234</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>5113</v>
+        <v>-423</v>
       </c>
       <c r="K35" t="n">
-        <v>4711</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3386</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3286</v>
+        <v>-3088</v>
       </c>
       <c r="N35" t="n">
-        <v>2949</v>
+        <v>-1688</v>
       </c>
       <c r="O35" t="n">
-        <v>-2693</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-2426</v>
+        <v>-500</v>
       </c>
       <c r="Q35" t="n">
-        <v>-2472</v>
+        <v>-500</v>
       </c>
       <c r="R35" t="n">
-        <v>2752</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2836</v>
+        <v>-4525</v>
       </c>
       <c r="T35" t="n">
-        <v>2294</v>
+        <v>-2775</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-1075</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Non cash Capital Related Government Assistance</t>
+          <t>Proceeds from Stock Plans</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>639</v>
+        <v>427</v>
       </c>
       <c r="C36" t="n">
-        <v>6094</v>
+        <v>427</v>
       </c>
       <c r="D36" t="n">
-        <v>1452</v>
+        <v>777</v>
       </c>
       <c r="E36" t="n">
-        <v>985</v>
+        <v>491</v>
       </c>
       <c r="F36" t="n">
-        <v>2211</v>
+        <v>491</v>
       </c>
       <c r="G36" t="n">
-        <v>1281</v>
+        <v>986</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -5926,388 +6248,406 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>512</v>
+      </c>
+      <c r="U36" t="n">
+        <v>503</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Interest Paid, Excluding Capitalized Interest, Operating Activities</t>
+          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>600</v>
+        <v>-617</v>
       </c>
       <c r="C37" t="n">
-        <v>1156</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1099</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>488</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>459</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Income Taxes Paid, Net</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="C38" t="n">
-        <v>1939</v>
+        <v>-870</v>
       </c>
       <c r="D38" t="n">
-        <v>1793</v>
+        <v>-1052</v>
       </c>
       <c r="E38" t="n">
-        <v>221</v>
+        <v>-678</v>
       </c>
       <c r="F38" t="n">
-        <v>1880</v>
+        <v>-618</v>
       </c>
       <c r="G38" t="n">
-        <v>1555</v>
+        <v>-1277</v>
       </c>
       <c r="H38" t="n">
-        <v>315</v>
+        <v>-444</v>
       </c>
       <c r="I38" t="n">
-        <v>1649</v>
+        <v>-220</v>
       </c>
       <c r="J38" t="n">
-        <v>1520</v>
+        <v>457</v>
       </c>
       <c r="K38" t="n">
-        <v>267</v>
+        <v>212</v>
       </c>
       <c r="L38" t="n">
-        <v>3960</v>
+        <v>-225</v>
       </c>
       <c r="M38" t="n">
-        <v>3326</v>
+        <v>-140</v>
       </c>
       <c r="N38" t="n">
-        <v>335</v>
+        <v>-281</v>
       </c>
       <c r="O38" t="n">
-        <v>1831</v>
+        <v>-666</v>
       </c>
       <c r="P38" t="n">
-        <v>1110</v>
+        <v>-900</v>
       </c>
       <c r="Q38" t="n">
-        <v>172</v>
+        <v>-815</v>
       </c>
       <c r="R38" t="n">
-        <v>1986</v>
+        <v>-527</v>
       </c>
       <c r="S38" t="n">
-        <v>574</v>
+        <v>605</v>
       </c>
       <c r="T38" t="n">
-        <v>211</v>
+        <v>629</v>
+      </c>
+      <c r="U38" t="n">
+        <v>726</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Disposal Group, Not Discontinued Operation, Gain (Loss) on Disposal</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>-8548</v>
       </c>
       <c r="C39" t="n">
-        <v>-5355</v>
+        <v>-1206</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>5738</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-196</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>11075</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>14867</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>8353</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>7511</v>
       </c>
       <c r="L39" t="n">
-        <v>-1072</v>
+        <v>7394</v>
       </c>
       <c r="M39" t="n">
-        <v>-1072</v>
+        <v>-982</v>
       </c>
       <c r="N39" t="n">
-        <v>-1121</v>
+        <v>-4665</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>-1863</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>-2056</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>-5962</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>-3674</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>-11220</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1573</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4764</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Asset Impairment Charges And Gain Loss On Disposal Of Property Plant And Equipment</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>-1115</v>
       </c>
       <c r="C40" t="n">
-        <v>465</v>
+        <v>2983</v>
       </c>
       <c r="D40" t="n">
-        <v>482</v>
+        <v>2892</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1444</v>
       </c>
       <c r="F40" t="n">
-        <v>2290</v>
+        <v>698</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1706</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>4208</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>-156</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-3523</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>-2795</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-2912</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>-298</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>-437</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1388</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2005</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>-1119</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>-673</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>-838</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>4542</v>
+      </c>
+      <c r="U40" t="n">
+        <v>7186</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale and Maturity of Other Investments</t>
+          <t>Capital Expenditures Incurred but Not yet Paid</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>3148</v>
       </c>
       <c r="C41" t="n">
-        <v>642</v>
+        <v>1949</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>5068</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>5155</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3932</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>6595</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>5544</v>
       </c>
       <c r="I41" t="n">
-        <v>375</v>
+        <v>5167</v>
       </c>
       <c r="J41" t="n">
-        <v>253</v>
+        <v>5234</v>
       </c>
       <c r="K41" t="n">
-        <v>116</v>
+        <v>5113</v>
       </c>
       <c r="L41" t="n">
-        <v>4880</v>
+        <v>4711</v>
       </c>
       <c r="M41" t="n">
-        <v>4775</v>
+        <v>3386</v>
       </c>
       <c r="N41" t="n">
-        <v>4682</v>
+        <v>3286</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2949</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>-2693</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>-2426</v>
       </c>
       <c r="R41" t="n">
-        <v>339</v>
+        <v>-2472</v>
       </c>
       <c r="S41" t="n">
-        <v>186</v>
+        <v>2752</v>
       </c>
       <c r="T41" t="n">
-        <v>20</v>
+        <v>2836</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2294</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Commercial Paper</t>
+          <t>Non cash Capital Related Government Assistance</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="C42" t="n">
-        <v>-3493</v>
+        <v>639</v>
       </c>
       <c r="D42" t="n">
-        <v>-1496</v>
+        <v>6094</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="F42" t="n">
-        <v>-7349</v>
+        <v>985</v>
       </c>
       <c r="G42" t="n">
-        <v>-2609</v>
+        <v>2211</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1281</v>
       </c>
       <c r="I42" t="n">
-        <v>-3944</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>-3944</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>-2930</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -6334,160 +6674,169 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Noncontrolling Interests</t>
+          <t>Interest Paid, Excluding Capitalized Interest, Operating Activities</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="C43" t="n">
-        <v>922</v>
+        <v>600</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1099</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="I43" t="n">
-        <v>2423</v>
+        <v>540</v>
       </c>
       <c r="J43" t="n">
-        <v>1573</v>
+        <v>968</v>
       </c>
       <c r="K43" t="n">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>252</v>
+      </c>
+      <c r="U43" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Long-term Debt</t>
+          <t>Income Taxes Paid, Net</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>904</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1939</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1793</v>
       </c>
       <c r="F44" t="n">
-        <v>2975</v>
+        <v>221</v>
       </c>
       <c r="G44" t="n">
-        <v>2975</v>
+        <v>1880</v>
       </c>
       <c r="H44" t="n">
-        <v>2537</v>
+        <v>1555</v>
       </c>
       <c r="I44" t="n">
-        <v>11391</v>
+        <v>315</v>
       </c>
       <c r="J44" t="n">
-        <v>10968</v>
+        <v>1649</v>
       </c>
       <c r="K44" t="n">
-        <v>10968</v>
+        <v>1520</v>
       </c>
       <c r="L44" t="n">
-        <v>6103</v>
+        <v>267</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3960</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3326</v>
       </c>
       <c r="O44" t="n">
-        <v>4974</v>
+        <v>335</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1831</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="R44" t="n">
-        <v>10247</v>
+        <v>172</v>
       </c>
       <c r="S44" t="n">
-        <v>10247</v>
+        <v>1986</v>
       </c>
       <c r="T44" t="n">
-        <v>10247</v>
+        <v>574</v>
+      </c>
+      <c r="U44" t="n">
+        <v>211</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>intc_ProceedsFromIssuanceOfCommonStockAndWarrants</t>
+          <t>Deferred Income Tax Expense (Benefit)</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>3737</v>
+        <v>-9</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>6368</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -6526,44 +6875,47 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Derivative Instrument, Financing Activities</t>
+          <t>Proceeds From Partner Contributions</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>3945</v>
+        <v>2064</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>3652</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2238</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>955</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>12278</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>11861</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -6590,13 +6942,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Payments of Dividends</t>
+          <t>Disposal Group, Not Discontinued Operation, Gain (Loss) on Disposal</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6606,61 +6961,64 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>-5355</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-1599</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>-1063</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-529</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>-2561</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>-2036</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>-1512</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>-4488</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-2986</v>
+        <v>-1072</v>
       </c>
       <c r="N47" t="n">
-        <v>-1487</v>
+        <v>-1072</v>
       </c>
       <c r="O47" t="n">
-        <v>-4231</v>
+        <v>-1121</v>
       </c>
       <c r="P47" t="n">
-        <v>-2821</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>-1411</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>-4215</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>-2811</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-1408</v>
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>Proceeds from Sale and Maturity of Other Investments</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6670,61 +7028,64 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>8249</v>
+        <v>642</v>
       </c>
       <c r="E48" t="n">
-        <v>8249</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>7079</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>7079</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>7079</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>11144</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>11144</v>
+        <v>375</v>
       </c>
       <c r="K48" t="n">
-        <v>11144</v>
+        <v>253</v>
       </c>
       <c r="L48" t="n">
-        <v>4827</v>
+        <v>116</v>
       </c>
       <c r="M48" t="n">
-        <v>4827</v>
+        <v>4880</v>
       </c>
       <c r="N48" t="n">
-        <v>4827</v>
+        <v>4775</v>
       </c>
       <c r="O48" t="n">
-        <v>5865</v>
+        <v>4682</v>
       </c>
       <c r="P48" t="n">
-        <v>5865</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5865</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>4194</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>4194</v>
+        <v>339</v>
       </c>
       <c r="T48" t="n">
-        <v>4194</v>
+        <v>186</v>
+      </c>
+      <c r="U48" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Finance Lease, Principal Payments</t>
+          <t>intc_ProceedsFromIssuanceOfCommonStockAndWarrants</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6734,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>3737</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -6749,22 +7110,22 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>-96</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>-96</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>-341</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-299</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>-299</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6782,13 +7143,16 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Contract with Customer, Liability</t>
+          <t>Proceeds from Derivative Instrument, Financing Activities</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -6798,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>3945</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -6822,37 +7186,40 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-1577</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>-1571</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>-1566</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-91</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>-161</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>-87</v>
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Divestiture Additions To Property Plant And Equipment Held For Sale</t>
+          <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6871,52 +7238,55 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-1599</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>-1063</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>-529</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-2561</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>-2036</v>
       </c>
       <c r="L51" t="n">
-        <v>-206</v>
+        <v>-1512</v>
       </c>
       <c r="M51" t="n">
-        <v>-206</v>
+        <v>-4488</v>
       </c>
       <c r="N51" t="n">
-        <v>-193</v>
+        <v>-2986</v>
       </c>
       <c r="O51" t="n">
-        <v>1118</v>
+        <v>-1487</v>
       </c>
       <c r="P51" t="n">
-        <v>682</v>
+        <v>-4231</v>
       </c>
       <c r="Q51" t="n">
-        <v>416</v>
+        <v>-2821</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>-1411</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>-4215</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>-2811</v>
+      </c>
+      <c r="U51" t="n">
+        <v>-1408</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Payments for Repurchase of Common Stock</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -6929,58 +7299,61 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>8249</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>8249</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>7079</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>7079</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>7079</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>11144</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>11144</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>11144</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4827</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4827</v>
       </c>
       <c r="O52" t="n">
-        <v>-2415</v>
+        <v>4827</v>
       </c>
       <c r="P52" t="n">
-        <v>-2415</v>
+        <v>5865</v>
       </c>
       <c r="Q52" t="n">
-        <v>-2301</v>
+        <v>5865</v>
       </c>
       <c r="R52" t="n">
-        <v>-12229</v>
+        <v>5865</v>
       </c>
       <c r="S52" t="n">
-        <v>-4229</v>
+        <v>4194</v>
       </c>
       <c r="T52" t="n">
-        <v>-4229</v>
+        <v>4194</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4194</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale and Maturity of Debt Securities, Available-for-sale</t>
+          <t>Increase (Decrease) in Contract with Customer, Liability</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -7017,34 +7390,37 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="O53" t="n">
-        <v>3457</v>
+        <v>-6</v>
       </c>
       <c r="P53" t="n">
-        <v>2126</v>
+        <v>-1577</v>
       </c>
       <c r="Q53" t="n">
-        <v>1232</v>
+        <v>-1571</v>
       </c>
       <c r="R53" t="n">
-        <v>5037</v>
+        <v>-1566</v>
       </c>
       <c r="S53" t="n">
-        <v>1303</v>
+        <v>-91</v>
       </c>
       <c r="T53" t="n">
-        <v>625</v>
+        <v>-161</v>
+      </c>
+      <c r="U53" t="n">
+        <v>-87</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Trading Securities Held-for-investment</t>
+          <t>Divestiture Additions To Property Plant And Equipment Held For Sale</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -7081,91 +7457,298 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>-206</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>-206</v>
       </c>
       <c r="O54" t="n">
-        <v>-26343</v>
+        <v>-193</v>
       </c>
       <c r="P54" t="n">
-        <v>-14637</v>
+        <v>1118</v>
       </c>
       <c r="Q54" t="n">
-        <v>-5981</v>
+        <v>682</v>
       </c>
       <c r="R54" t="n">
-        <v>-14744</v>
+        <v>416</v>
       </c>
       <c r="S54" t="n">
-        <v>-11429</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>-3897</v>
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>Payments for Repurchase of Common Stock</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-2415</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-2415</v>
+      </c>
+      <c r="R55" t="n">
+        <v>-2301</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-12229</v>
+      </c>
+      <c r="T55" t="n">
+        <v>-4229</v>
+      </c>
+      <c r="U55" t="n">
+        <v>-4229</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Proceeds from Sale and Maturity of Debt Securities, Available-for-sale</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3457</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2126</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1232</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5037</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1303</v>
+      </c>
+      <c r="U56" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Payments to Acquire Trading Securities Held-for-investment</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-26343</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-14637</v>
+      </c>
+      <c r="R57" t="n">
+        <v>-5981</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-14744</v>
+      </c>
+      <c r="T57" t="n">
+        <v>-11429</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-3897</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>Proceeds from Sale and Maturity of Debt and Equity Securities, FV-NI, Held-for-investment</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
         <v>18813</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q58" t="n">
         <v>12936</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R58" t="n">
         <v>6777</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S58" t="n">
         <v>11227</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T58" t="n">
         <v>7430</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U58" t="n">
         <v>3660</v>
       </c>
     </row>
